--- a/food-bangalore-audits/Food-Bangalore-ALL-IN-ONE.xlsx
+++ b/food-bangalore-audits/Food-Bangalore-ALL-IN-ONE.xlsx
@@ -15,10 +15,16 @@
     <sheet name="Expected ROI" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Audit Basis (sources)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Skills Used" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Findings (severity+evidence)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Opportunity Score" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Coverage (measured vs not)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Evidence Register" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leads'!$A$1:$O$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Emails'!$A$1:$F$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Findings (severity+evidence)'!$A$1:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Evidence Register'!$A$1:$E$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -55,7 +61,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +86,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F3FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -130,6 +161,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -556,7 +602,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>audits/&lt;brand&gt;-audit-report.pdf — attractive 2-page format (you vs competitor, 3 leaks, roadmap, ROI, audit basis, CTA)</t>
+          <t>audits/&lt;brand&gt;-paid-media-measurement-audit.pdf — 7-page Paid Media &amp;amp; Measurement Audit: cover metrics, contents+method, live ad account, severity-ranked findings with the raw measurement quoted, evidence register, opportunity score /20, qualification, effort-ordered next steps</t>
         </is>
       </c>
     </row>
@@ -616,7 +662,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Meta Ad Library — verified for Licious (Library ID 983369480870934, live since 15 Apr 2026); others noted where not verified</t>
+          <t>Meta Ad Library — verified live for Akshayakalpa (4 to 5 creatives, running since 19 May 2026, library IDs recorded) and Licious (Library ID 983369480870934, ≈550 live); other brands returned no inventory and are reported as not measured, never as zero</t>
         </is>
       </c>
     </row>
@@ -640,7 +686,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Live raw HTML + rendered pages captured 02 OCT 2026 (tokens, GTM/GA4 IDs, defects quoted verbatim)</t>
+          <t>Live HTTP headers + HTML captured 02 OCT 2026 (GTM/GA4/Ads/pixel IDs, platform, redirects, defects quoted verbatim)</t>
         </is>
       </c>
     </row>
@@ -700,7 +746,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Where something was NOT verified, the audit says so explicitly (e.g. Third Wave: Google verified at 0, Meta not checked)</t>
+          <t>Where something was NOT verified it is reported as unavailable or not measured — never as zero, and never estimated. A tag is only called absent when a second method confirmed it; otherwise it reads unconfirmed</t>
         </is>
       </c>
     </row>
@@ -717,6 +763,6136 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Score /4</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>What the score is based on</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Overall /20</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Grade note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Meta spend verified live; site tag not confirmed by one method.</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>serious paid spend meeting fixable configuration problems</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>No confirmed on-site pixel or server-side path.</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>serious paid spend meeting fixable configuration problems</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Placeholder international contact block on an India-facing site.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>serious paid spend meeting fixable configuration problems</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>No CDN, no cache layer, no HSTS on the largest spender.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>serious paid spend meeting fixable configuration problems</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Category leader, publicly stated growth target, live paid spend.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>serious paid spend meeting fixable configuration problems</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI pixel observed; Google and Meta tag set not fully confirmed.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>clean foundations; the upside is measurement and social proof, not repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Conversion definitions across surfaces not verifiable publicly.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>clean foundations; the upside is measurement and social proof, not repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Heritage brand, coherent storefront, structured data in place.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>clean foundations; the upside is measurement and social proof, not repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Best header and CDN posture measured in this group.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>clean foundations; the upside is measurement and social proof, not repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Festive and gifting demand with fifty-eight live creatives.</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>clean foundations; the upside is measurement and social proof, not repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Tag set not confirmed on the crawl.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>brand strength ahead of its paid and measured presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Small paid footprint; D2C path not verified.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>brand strength ahead of its paid and measured presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Established retail brand, consistent identity.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>brand strength ahead of its paid and measured presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Managed platform; no defects observed.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>brand strength ahead of its paid and measured presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Large retail base with almost no paid demand generation.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>brand strength ahead of its paid and measured presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>No tag set confirmed; only platform and headers measured.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>a strong business leaving paid learning on the table</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>One live creative means little to observe.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>a strong business leaving paid learning on the table</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Established brand, self-hosted site, consistent identity.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>a strong business leaving paid learning on the table</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Fast LiteSpeed cache, but wildcard CORS and report-only CSP.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>a strong business leaving paid learning on the table</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Profitable at scale with almost no paid testing.</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>a strong business leaving paid learning on the table</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>One analytics tag observed; ads and pixel tags not visible on the root.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>strong operation, under-instrumented marketing surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Ordering flow is separate from the marketing root; not confirmed.</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>strong operation, under-instrumented marketing surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Consistent design tokens and published brand system.</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>strong operation, under-instrumented marketing surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Fast static delivery; tag changes gated behind deploys.</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>strong operation, under-instrumented marketing surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Retail scale plus an untapped contract channel.</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>strong operation, under-instrumented marketing surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Tag layer unconfirmed by the methods used.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>live paid spend with an unverified measurement path</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Unknown until the browser check is run.</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>live paid spend with an unverified measurement path</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Strong heritage identity, modern storefront.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>live paid spend with an unverified measurement path</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Standard Shopify stack; no defects observed.</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>live paid spend with an unverified measurement path</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Daily-consumption category with seventy-seven live creatives.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>live paid spend with an unverified measurement path</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Tag layer not measured on this crawl.</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>clean platform, unverified measurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Not verified publicly.</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>clean platform, unverified measurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Clean managed storefront with a consistent theme.</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>clean platform, unverified measurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Cloudflare plus Shopify; no defects observed.</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>clean platform, unverified measurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Trust-driven category where paid spend can compound.</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>clean platform, unverified measurement</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Four tag families live on the site root, confirmed by ID.</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>measurement is in place; the remaining work is consolidation and reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>One observed Meta pixel across ≈550 ads; segments not separable.</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>measurement is in place; the remaining work is consolidation and reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Canonical host, brand and creative inventory all aligned.</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>measurement is in place; the remaining work is consolidation and reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Next.js on a clean redirect chain; headers not fully measured.</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>measurement is in place; the remaining work is consolidation and reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Category leader with paid spend at real scale.</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>measurement is in place; the remaining work is consolidation and reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Container, ads tag and pixel all present and independent.</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>measurement is sound; hosting and speed are the drag</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Tags installed; conversion definitions not verifiable publicly.</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>measurement is sound; hosting and speed are the drag</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Canonical host redirects correctly; brand creative is consistent.</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>measurement is sound; hosting and speed are the drag</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>No cache layer and no security headers on nginx.</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>measurement is sound; hosting and speed are the drag</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Occasion-led demand with thirty-five live creatives.</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>measurement is sound; hosting and speed are the drag</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>No tag set confirmed; platform measured only.</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>a strong brand leaving its digital front door unfinished</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>No live paid surface to observe.</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>a strong brand leaving its digital front door unfinished</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Title tag contradicts the brand on the homepage.</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>a strong brand leaving its digital front door unfinished</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Standard Shopify behind Cloudflare; redirect correct.</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>a strong brand leaving its digital front door unfinished</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Strong offline brand with an under-built digital surface.</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>a strong brand leaving its digital front door unfinished</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Measurement integrity</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Tag set not confirmed on the crawl.</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>small fixes standing between spend and conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Conversion observability</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Small live footprint; conversion path has a broken page.</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>small fixes standing between spend and conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Brand consistency</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Storefront consistent with the brand identity.</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>small fixes standing between spend and conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Technical health</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Standard Shopify stack; one broken page observed.</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>small fixes standing between spend and conversions</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Commercial fit</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Dessert and gifting demand with a franchise channel.</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>small fixes standing between spend and conversions</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Surface</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Method / reason</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Crawl date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 400</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — verified ad by ad</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 58</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — OpenAI ads pixel MsnBMqKgkHz42jqdSfTfFQ observed in the …</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 3</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 1</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 56</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — GA4 G-EN77D2S0YH observed on the site root; Google Ads tag …</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 77</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 30</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 300</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 550</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — GTM-KVBCJN · GA4 G-YN0TX18PEE · Google Ads AW-871318622 · …</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 35</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — GTM-MQQF2MXB · Google Ads AW-618150299 · Meta pixel …</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>no published figure is quoted in this report</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — count recorded</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — www.thirdwavecoffeeroasters.com — the domain string, not the …</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Google creative inventory</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED — 11</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India), 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Meta ad inventory</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term on the crawl date</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root, 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Checkout and order flow</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>NOT MEASURED</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>outside the site root; not crawled</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend, ROAS, CPA</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>private to the advertiser; no public source</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>the brand's own published pages and results, as reported</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Value observed</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>≈400 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Started 19 May 2026 (2 ads) · 24 Jun 2026 · 12 Aug 2026 (9 ads) · 16 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Apache 2.4.52 (Ubuntu) with WordPress; no CDN, no cache-control, no HSTS observed</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>none published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>published:  approx Rs 45-46 Cr monthly run-rate</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>≈58 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI ads pixel MsnBMqKgkHz42jqdSfTfFQ observed in the storefront source</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Shopify behind Cloudflare; theme 162670313687</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>none published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>published: heritage sweet house, now D2C + retail</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>≈3 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Wix behind Varnish (x-wix-request-id observed)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>customercare@milkymist.com</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>customercare@milkymist.com</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>1 creative live, region India</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>WordPress on LiteSpeed; cache HIT observed</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>customercare@idfreshfood.com</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>revenue approx Rs 681.4 Cr · profit after tax approx Rs 25.87 Cr</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>≈56 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>GA4 G-EN77D2S0YH observed on the site root; Google Ads tag not observed on the root</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Static build on Amazon S3 behind CloudFront; asset last-modified 22 Sep 2026</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>none published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>900,000+ cups per day · 150+ stores · 8,100+ workplaces · 9,000+ pincodes (own structured data)</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>≈77 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>unconfirmed — selectors for tag manager and pixel returned no result on the crawls attempted</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>customercare@cothas.com</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>customercare@cothas.com</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>≈30 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>not measured on this crawl — reported as unavailable</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Shopify behind Cloudflare; theme 124761112618</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>hello@earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>hello@earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>≈300 in the India region on 2 October 2026</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>≈550 for the brand term; library ID 983369480870934 observed</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>GTM-KVBCJN · GA4 G-YN0TX18PEE · Google Ads AW-871318622 · Meta pixel 378591842535023</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Next.js front-end; apex 301 → www</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>none published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>published FY25: revenue approx Rs 795 Cr</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>≈35 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>GTM-MQQF2MXB · Google Ads AW-618150299 · Meta pixel 3996239487069441</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>WordPress on nginx</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>none published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>not used in this report</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Google — no live creative found for the brand term in the India region on the crawl date</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>www.thirdwavecoffeeroasters.com — the domain string, not the brand name</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Shopify behind Cloudflare; theme 133405212742</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>orders@thirdwavecoffee.in</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>orders@thirdwavecoffee.in</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Google creatives</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region India)</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>≈11 creatives, region India</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country India)</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>no inventory returned for the brand term</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Measurement tags on the site root</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>HTML inspection of the site root</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>not measured</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Site platform and headers</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Live HTTP response of the site root</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Shopify behind Cloudflare; theme 175376138404</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Published contact</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own contact and policy pages</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>vipul@frozenbottle.in</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend / ROAS / CPA</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>unavailable — not estimated</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Published commercial figures</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>The brand's own published pages and results</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>vipul@frozenbottle.in</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>2 October 2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -810,7 +6986,7 @@
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
-          <t>Audit PDF</t>
+          <t>Audit PDF (7-page evidence format)</t>
         </is>
       </c>
       <c r="N1" s="5" t="inlineStr">
@@ -881,7 +7057,7 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>audits/akshayakalpa-organic-audit-report.pdf</t>
+          <t>audits/akshayakalpa-organic-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
@@ -952,7 +7128,7 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>audits/anand-sweets-audit-report.pdf</t>
+          <t>audits/anand-sweets-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
@@ -1023,7 +7199,7 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>audits/milky-mist-audit-report.pdf</t>
+          <t>audits/milky-mist-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
@@ -1094,7 +7270,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>audits/id-fresh-food-audit-report.pdf</t>
+          <t>audits/id-fresh-food-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
@@ -1165,7 +7341,7 @@
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>audits/chai-point-audit-report.pdf</t>
+          <t>audits/chai-point-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
@@ -1232,7 +7408,7 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>audits/cothas-coffee-audit-report.pdf</t>
+          <t>audits/cothas-coffee-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
@@ -1303,7 +7479,7 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>audits/early-foods-audit-report.pdf</t>
+          <t>audits/early-foods-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
@@ -1374,7 +7550,7 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>audits/licious-audit-report.pdf</t>
+          <t>audits/licious-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -1445,7 +7621,7 @@
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>audits/the-baker-s-dozen-audit-report.pdf</t>
+          <t>audits/the-baker-s-dozen-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
@@ -1516,7 +7692,7 @@
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>audits/third-wave-coffee-audit-report.pdf</t>
+          <t>audits/third-wave-coffee-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
@@ -1587,7 +7763,7 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>audits/frozen-bottle-audit-report.pdf</t>
+          <t>audits/frozen-bottle-paid-media-measurement-audit.pdf</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
@@ -7469,7 +13645,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Google Ads Transparency + Meta Ad Library: live counts, advertiser entities, destinations, durations</t>
+          <t>Google Ads Transparency (region IN) + Meta Ad Library (country IN): live counts and, where open, individual creatives with running-since dates</t>
         </is>
       </c>
     </row>
@@ -7588,11 +13764,1839 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Attractive 2-page Smart Pursuit format with audit-basis box + CTA</t>
+          <t>7-page Paid Media &amp;amp; Measurement Audit: metric cards, method, live ad account, coverage table, severity findings with quoted evidence, evidence register, opportunity score, qualification, next steps</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Evidence (raw measurement)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Why it matters (analysis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>The site footer carries an international placeholder phone number and address</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>footer text:  0123.456.789 – 2 Queen Street, California
+site:        akshayakalpa.org (India-facing)
+published:   Tiptur farms, Karnataka; corporate office Bengaluru</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>A placeholder contact block on a site taking dairy subscriptions actively damages trust and is trivially fixable. Every other finding in this report is secondary to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>The largest paid footprint in the category runs on an uncached, CDN-less server</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>server:        Apache/2.4.52 (Ubuntu) + WordPress
+cache-control: absent
+strict-transport-security: absent
+cdn:           none observed</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Roughly four hundred creatives send traffic into a server with no cache layer. Measured at the origin, this is the slowest configuration in this group of eleven, and slow origins depress landing-page conversion regardless of creative quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Meta ads are live and verifiable, but no on-site tag could be confirmed from the root</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>meta ads:   live — running since 19 May 2026, 24 Jun 2026, 12 Aug 2026, 16 Sep 2026
+site root:  no meta pixel selector resolved on the crawl
+method:     single-method result — not asserted as absence</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Spend is proven live on Meta. If the pixel is not firing on the site root, that spend is being optimised on partial signal. A two-minute browser check with a pixel helper settles it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>The brand is being sold through third-party distribution creative as well as its own</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>creative observed:  Swiggy Instamart — organic protein, Insta-delivered
+creative observed:  Zepto — quick-commerce placements under the term
+brand account:       separate creatives, running since May–Sep 2026</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Quick-commerce placements sell the product but own the customer relationship. Neither surface passes a first-party identifier back, which makes the brand's own click-ID continuity more, not less, important.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Meta creative is farm-to-door storytelling, consistently executed</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>creative 1: 'Milk from healthy cows fed on organic fodder grown in chemical free soil.'
+creative 2: 'From nutritious soil to healthy cows, we ensure every drop of milk is pure and organic.'
+creative 3: high-protein paneer, organic milk and curd</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>The creative platform is coherent across months. The gap is not in the message; it is in what happens after the click.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Commercial scale is real and publicly stated</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>published:  approx Rs 45-46 Cr monthly run-rate
+published:  FY26 target approx Rs 550 Cr
+certification: APEDA-certified organic</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>This is not a brand testing paid media. At this scale, measurement gaps are expensive rather than inconvenient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>An OpenAI advertising pixel is live on the storefront</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>pixel observed:  MsnBMqKgkHz42jqdSfTfFQ (OpenAI ads)
+context:        58 live Google creatives alongside
+platform:       Shopify + Cloudflare, theme 162670313687</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Testing a new ad surface this early is a genuine advantage — most brands in this category have not started. The question to answer next is whether that pixel is tied to the same conversion definition as the Google account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>The public rating signal is thin for the level of spend</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>aggregateRating: 4.4
+rating count:     250
+live creatives:   ≈58</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Two hundred and fifty ratings is a small social-proof base for a heritage brand running this much creative. Review volume is usually the cheapest available conversion lever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>A single shared inbox carries all published contact</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>published contact: care@anandsweets.net
+separate retail, gifting or corporate contacts: none published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Order queries, corporate gifting enquiries and complaints arriving in one inbox is a routing problem, not a headcount problem. A gifting enquiry is worth many times a cake query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Technical and security posture is the best in this group</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>strict-transport-security: max-age=7889238
+content-security-policy: block-all-mixed-content; frame-ancestors 'none'
+x-frame-options: DENY
+x-content-type-options: nosniff
+cdn: cloudflare (cf-cache-status DYNAMIC)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Headers like these are set by people who care. Measurement discipline, not infrastructure, is where the remaining upside sits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Heritage positioning is a real commercial asset</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>founded: 1988
+headquarters: Dickenson Road, Bengaluru 560042
+published: heritage sweet house, now D2C + retail</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Thirty-eight years of brand equity is not something paid media can buy. The audit's job is to make sure paid traffic converts against that equity rather than diluting it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Three live creatives for a dairy brand with national retail distribution</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>google creatives live: 3 (region India)
+comparison in this set: one competitor runs ≈400
+platform:              Wix behind Varnish</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Retail distribution and paid demand are two different engines. Three creatives cannot generate pull for a brand that is already on shelves — the first task is deciding which products to put paid behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>The site runs on a site-builder stack rather than a commerce stack</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>platform: Wix
+serving layer: Varnish
+contact: customercare@milkymist.com</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Wix is fast to launch and hard to instrument precisely. If direct-to-consumer is a real ambition, the measurement and checkout stack — not the design — is the constraint to plan around.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>The contact path is a single support inbox</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>published contact: customercare@milkymist.com
+separate distributor or trade contact: not published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>For a brand in retail, distributor and trade enquiries are the highest-value inbound. They should be separable from consumer complaints on day one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Canonical host handling is correct</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>milkymist.com → 301 → www.milkymist.com</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>One fewer thing to fix. Paid and organic traffic land on a single host.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>One live Google creative against a Rs 681 Cr revenue base</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>google creatives live: 1 (region India)
+published FY25:         revenue approx Rs 681.4 Cr · PAT approx Rs 25.87 Cr
+platform:               WordPress + LiteSpeed</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>A profitable business at this scale with a single live Google creative is not under-spending — it is under-testing. There is no channel data to learn from at one creative, and the first three to five test cells are where the learning is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Wildcard CORS is switched on for the whole site</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>access-control-allow-origin: *
+content-security-policy: report-only</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>A wildcard origin lets any site call the domain's resources. For a brand with a logged-in or form-based surface this is a security setting, not a performance one, and it is a single line in the server config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Content-security-policy is report-only, so it enforces nothing</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>content-security-policy: report-only
+cache: LiteSpeed cache HIT (working correctly)</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Report-only mode is the right way to roll a policy out, and it is the wrong place to stop. The cache layer is doing its job; the security policy is not yet doing anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>A single support inbox carries all published contact</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>published contact: customercare@idfreshfood.com</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>With modern trade, HoReCa and D2C running side by side, one public address under-serves the highest-value partner conversations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Hosting is well configured for speed</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>server stack: WordPress on LiteSpeed
+cache status:  HIT
+implication:   full-page cache serving correctly</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>LiteSpeed with a cache hit is a fast, cheap configuration — better than most of this group. The technical platform is not the constraint here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Only one measurement tag is observable against fifty-six live creatives</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>ga4:          G-EN77D2S0YH (site root)
+google ads:   not observed on the site root
+meta pixel:   not observed on the site root
+live creatives: ≈56 (region India)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>If the Google Ads tag sits on the ordering sub-domain rather than the marketing root, it would not appear here. Either way, the observable measurement surface is one analytics tag for a business running paid media at scale — worth confirming with a browser check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>The site is a static build, so any tag change needs a deploy</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>host:          Amazon S3 + CloudFront
+last-modified: 22 Sep 2026 (static assets)
+stack:         Tailwind v4.3.3 front-end</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Static delivery is fast and cheap, and it is the right call for a store locator. The trade-off is that marketing tags cannot be added by a marketer — every experiment queues behind an engineering release unless a tag manager is present in the build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Bulk and workplace demand is a higher-value channel than the retail creative mix implies</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>published pages: events and bulk orders
+published scale:  8,100+ workplaces, 9,000+ pincodes
+live creatives:   ≈56, predominantly retail coffee</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Workplace coffee is a contract business with very different economics from a cup. If bulk-order pages were reached by a dedicated campaign, the same spend would face less competition and a longer customer lifetime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Customer care runs through a single published inbox</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>published contact: customercare@chaipoint.com
+separate bulk or franchise contact: not published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Routine queries and B2B enquiries share one address. The B2B enquiry is the one that should never wait in the same queue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>The scale story is machine-readable and quotable</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>json-ld: 900,000+ cups per day
+json-ld: 150+ stores · 8,100+ workplaces · 9,000+ pincodes</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Structured data this specific is a B2B weapon — workplace and bulk-order demand can be qualified by pincode before a call. Almost no consumer brand in this category publishes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Brand design tokens are applied consistently</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>brand: #18289c
+accent: #ff6c22
+framework: Tailwind v4.3.3</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Colour and type are consistent between the site and the published brand system. Creative-to-landing continuity has a solid base to build on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Seventy-seven live creatives run against an unconfirmed tag layer</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>google creatives live: 77 (region India)
+tag inspection:        no tag-manager or pixel selector resolved
+site platform:         Shopify
+confidence:            single method — not asserted as absence</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Either the tags are injected in a way a static fetch cannot see, or paid traffic is landing on a storefront whose conversion signal is thinner than the spend implies. A browser-based check with a tag assistant settles it in minutes, and it is the first thing to do.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>A modern storefront on a heritage brand without a confirmed measurement layer</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>platform: Shopify
+contact:  customercare@cothas.com</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>A Shopify storefront is the easiest platform in this set on which to install measurement — the tags are usually a two-minute app install. That makes the unconfirmed result more surprising, not less.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Subscription and repeat-purchase mechanics are the natural fit for this category</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>category: filter coffee, daily household consumption
+inventory: 77 live creatives
+tag layer: unconfirmed</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Daily-consumption categories live or die on repeat rate. Without a confirmed tag layer, repeat behaviour cannot be measured or retargeted — which is where the 77 creatives should be pointed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>One shared inbox for retail, trade and complaints</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>published contact: customercare@cothas.com
+separate wholesale contact: none published on the pages reviewed</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Filter coffee has a strong HoReCa and wholesale channel. Trade enquiries should not queue behind retail complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Heritage is the brand's sharpest asset</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>founded:  1948
+facility:  Jigani, Karnataka 562105
+category:  filter coffee, South Indian household staple</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Seventy-eight years of household familiarity is rare in this market. The storefront is modern; the paid strategy should be playing the heritage card harder than it appears to be.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Thirty live creatives on a storefront whose measurement surface was not verified</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>google creatives live: ≈30 (region India)
+platform:              Shopify + Cloudflare, theme 124761112618
+tag measurement:       not performed on this crawl — unavailable</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>The inventory is small enough that a single measurement error costs real money proportionally. Verifying the tag layer is the first task, and the platform makes it easy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Category fit is strong but conversion depends on trust signals</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>category: early-years and child nutrition
+contact:  hello@earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Parents do not buy child nutrition from an ad alone — they buy from a brand that looks accountable. Reviews, ingredient sourcing and a visible support path are the conversion levers that make the same thirty creatives perform better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>A single inbox carries the published contact path</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>published contact: hello@earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>For a young brand, one inbox is a reasonable choice at low volume. It becomes a bottleneck at exactly the moment paid media starts working, so plan the split before it is urgent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>The storefront runs on a fully managed stack</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>platform: Shopify
+theme:    124761112618
+cdn:      Cloudflare (cf-cache-status observed)</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Managed hosting removes whole categories of technical risk. There is nothing structurally wrong to fix here — the question is purely whether the paid signal is complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Roughly 550 Meta ads run against a single observed on-site pixel ID</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>meta inventory:  ≈550 live ads for the brand term
+on-site pixel:   378591842535023  (one ID observed in page source)
+library id:      983369480870934</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>If web, app and retail audiences are all being built from the one observed ID, those audiences will overlap and segment-level ROAS cannot be read out of the pixel. A second dedicated pixel per destination is configuration, not a rebuild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Platform ad counts differ sharply and should be read as upper bounds</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>google creatives:  ≈300 (region India)
+meta ads:           ≈550 (keyword term, India)
+difference:         ~1.8x between platforms</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Keyword-based Meta counts can include third-party distribution of the same product. Treat the Meta number as an upper bound until the advertiser's own account confirms it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Canonical host handling is correct</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>licious.in → 301 → www.licious.in
+canonical host: www (consistent)</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Apex-to-www redirection is clean, so paid traffic and organic signals land on one host. This is one fewer thing to fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>All four tag families are present and consistent</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>container:  googletagmanager.com/gtm.js?id=GTM-KVBCJN
+analytics:  GA4 G-YN0TX18PEE
+google ads: AW-871318622
+meta pixel: 378591842535023</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>The measurement layer is the most complete in this group of eleven brands. The opportunity for Licious is consolidation and reporting discipline, not installation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>FY25 results put paid efficiency at the centre of the business</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>published FY25: revenue approx Rs 795 Cr
+disclosed result:  loss approx Rs 218.3 Cr
+context:          listed company, results publicly reported</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>A business at this scale with that result cannot treat paid media as a side channel. Loss reduction is a measurement problem as much as a media-buying problem — which makes the tag stack above the most valuable asset in the account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Well-built tag stack served by a site with no cache layer and no security headers</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>tags:            GTM-MQQF2MXB · AW-618150299 · pixel 3996239487069441
+strict-transport-security: absent
+cache-control:   absent
+x-frame-options: absent
+server:          nginx (WordPress)</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Measurement is installed the right way — container, ads tag and pixel all present. The infrastructure under it is the weakest part of an otherwise tidy setup, and caching plus four response headers is hours of work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Thirty-five creatives is enough to learn from and small enough to consolidate quickly</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>google creatives live: ≈35 (region India)
+ads tag present:        AW-618150299</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>At this footprint, a single tidy campaign structure with clean naming will beat more creative volume. The measurement is already in place to prove it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>No cache headers means every visit is served cold</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>cache-control: absent
+cdn:           none observed
+server:        nginx</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>Adding a cache layer and cache-control headers is a hosting change, not a development project. For a bakery where demand spikes around occasions, cold origin responses are exactly when speed matters most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Security headers are missing across the board</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>strict-transport-security: absent
+x-frame-options: absent
+x-content-type-options: absent
+content-security-policy: absent</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>None of these is exotic. Four directives in the server config close the gap and cost nothing to run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>One published inbox covers retail and celebration orders</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>published contact: fresh@thebakersdozen.in</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>Celebration and bulk orders are the high-ticket path for a bakery. Routing them separately from general enquiries protects the revenue that matters most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Tag ordering and coverage look correct</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>container:   GTM-MQQF2MXB
+ads tag:     AW-618150299
+meta pixel:  3996239487069441</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>All three families are present and independent, which is the pattern you want when paid spend sits across Google and Meta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>The homepage title tag is the domain string rather than the brand name</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>title tag:  www.thirdwavecoffeeroasters.com
+platform:   Shopify + Cloudflare, theme 133405212742</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>The title tag is what appears in the browser tab, in search results and in shared links. A domain string there wastes every impression the brand earns, and it is a two-minute theme edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>No live Google creative was found for the brand term</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>google ads transparency: 0 creatives (region India, brand term)
+competitors in this set:   1 to 400 creatives live</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>A brand with this much physical presence does not need to buy search for its own name, but the absence of any live inventory means there is no paid surface at all for new-city or new-product demand. That is a choice worth making explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>The storefront is otherwise well built</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>platform: Shopify behind Cloudflare
+theme:    133405212742
+canonical host: apex 301 → www</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>The stack is standard and the redirect is clean. The visible gap is presentation and paid presence, not engineering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Contact is a single orders address</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>published contact: orders@thirdwavecoffee.in</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Cafes, online orders, franchise enquiries and events are different businesses. One address for all of them loses the enquiry that is worth the most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>The physical brand is stronger than the digital surface implies</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>category: specialty coffee, Bengaluru
+platform: Shopify storefront
+paid inventory: none found on the crawl date</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>Cafe footfall and specialty positioning are real assets. The website and the paid surface are not yet carrying that equity — which is an opportunity, not a criticism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>The FAQ page returns a 404 error</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>url:    frozenbottle.com/pages/faq
+status: HTTP 404
+context: linked from the storefront navigation</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Frequently-asked questions are where dessert and gifting customers resolve delivery doubts. A dead page is a lost order, and on Shopify it is usually a two-minute fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Eleven live creatives is below the learning threshold for this category</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>google creatives live: ≈11 (region India)
+category:              desserts, ice cream and gifting</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>Eleven creatives across any meaningful audience set will not separate creative from audience effects. Two clean tests would tell more than eleven undifferentiated ads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>One published contact for orders and franchise enquiries</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>published contact: vipul@frozenbottle.in</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Franchise enquiries and customer orders in one place makes neither measurable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Franchise demand has a published path</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>published: franchise page on the storefront
+contact:   vipul@frozenbottle.in</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>A public franchise page is a growth channel in itself — franchise enquiries have a very different value from dessert orders and should be measured separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Platform hygiene is otherwise standard and safe</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>platform: Shopify + Cloudflare
+theme:    175376138404</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>There is nothing structurally wrong with the site. The fixes in this report are content and configuration, not architecture.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F57"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/food-bangalore-audits/Food-Bangalore-ALL-IN-ONE.xlsx
+++ b/food-bangalore-audits/Food-Bangalore-ALL-IN-ONE.xlsx
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>MEASURED — verified ad by ad</t>
+          <t>MEASURED — 3</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Started 19 May 2026 (2 ads) · 24 Jun 2026 · 12 Aug 2026 (9 ads) · 16 Sep 2026</t>
+          <t>3 live creatives from the brand page, running since 19 May 2026 (2 creatives, 2 variants each) and 24 Jun 2026 (1 creative, 2 variants)</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -7856,7 +7856,7 @@
           <t>Hi team,
 I audit paid media for food brands from Bengaluru. Your footprint is the biggest I found in this category: ~400 live Google creatives under Akshayakalpa Farms and Foods Pvt Ltd. The product story behind it is world-class - 4C farm chilling, 24-36 hours to doorstep vs the 72-96 hour industry norm, APEDA certified.
 One thing you can check in 30 seconds: the footer of akshayakalpa.org currently contains template placeholder text - '0123.456.789 - 2 Queen Street, California, USA'. Your paid traffic lands on that page. It is a small fix and a direct trust cost while it is live.
-Attached is a 2-page audit with 3 fixes, including what I would do with ~400 creatives to make them learn faster than they spend. Worth 15 minutes?
+Attached is the 7-page Paid Media and Measurement Audit, including what I would do with ~400 creatives to make them learn faster than they spend. Worth 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220
 P.S. I am writing to your published support address because the site does not list a marketing or partner contact - that is itself one of the findings.</t>
         </is>
@@ -7992,7 +7992,7 @@
           <t>Hi team,
 I run paid-media audits for Bengaluru food brands. I checked your live footprint: 58 Google creatives under Anand Sweets &amp; Savouries LLP, and Google shows you as a Verified advertiser - a real asset in mithai, where trust decides the order.
 The problem: your own top banner tells every paid visitor that Bangalore delivery takes up to 3 days and sends same-day buyers to Swiggy, Zomato or Ownly. That is the exact moment - festive, urgent, gift-driven - where mithai margins live, and it is being handed to an aggregator.
-Attached is a 2-page audit with 3 fixes. Open to a 15-minute call?
+Attached is the 7-page Paid Media and Measurement Audit. Open to a 15-minute call?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -8127,7 +8127,7 @@
           <t>Hi team,
 I run paid-media audits for food brands from Bengaluru. I checked your live presence this week: Milky Mist Dairy Food Limited shows 3 live Google creatives - while the corporate site carries a full IPO section, SEBI Reg 46 disclosures and investor pages.
 That gap matters now: paneer, curd, ghee and cheese searches are high-intent purchase moments, and today they are being answered by Amul, Nandini and quick-commerce private labels. Before a listing, demand durability is part of the story you will be asked about.
-Attached is a 2-page audit with 3 fixes. Open to 15 minutes?
+Attached is the 7-page Paid Media and Measurement Audit. Open to 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -8262,7 +8262,7 @@
           <t>Hi team,
 I run paid-media audits for food brands from Bengaluru. I checked your live footprint this week: Google Ads Transparency shows one live creative for idfreshfood.com, running under Blink Digital India Pvt Ltd.
 That is remarkable for a brand at INR 681 Cr revenue with an IPO in view - and it means every 'idli batter home delivery', 'malabar parota online' or 'preservative-free batter' search is being answered by quick-commerce and smaller D2C brands, not by you.
-I have attached a 2-page audit with 3 fixes, including the subscription engine that would add recurring revenue before your IPO window. 15 minutes this week?
+I have attached the 7-page Paid Media and Measurement Audit, including the subscription engine that would add recurring revenue before your IPO window. 15 minutes this week?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -8397,7 +8397,7 @@
           <t>Hi team,
 I audit paid media for Bengaluru food brands. I checked your live footprint: 56 Google creatives under Mountain Trail Foods, a genuinely modern site (GA4 G-EN77D2S0YH), and the numbers you publish are strong - 150+ stores, 900,000 cups a day, 8,100 workplace clients.
 Here is the leak: the B2B side - your highest-value line - has no paid funnel. No 'book a demo' path for office admins searching for tea vending, while your Brewing Bot (real tea leaves, not premix) is a genuinely superior product to every coffee-only incumbent.
-Attached: a 2-page audit with 3 fixes. Worth 15 minutes?
+Attached: the 7-page Paid Media and Measurement Audit. Worth 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -8531,7 +8531,7 @@
           <t>Hi team,
 I audit paid media for Bengaluru food brands. I inspected your live footprint this week: 77 Google creatives running under Freeflow Creative Services, including Local store ads like your HMT Road Mathikere store. Genuinely good work - most heritage brands your age run zero paid.
 The gap: a cafe owner searching 'coffee vending machine', a household buying filter coffee, and someone near a CoCo outlet all land on the same destination. Three buyers, one page.
-Attachment: a 2-page audit with 3 fixes. Worth a short call?
+Attachment: the 7-page Paid Media and Measurement Audit. Worth a short call?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -8666,7 +8666,7 @@
           <t>Hi team,
 I audit paid media for Bengaluru food brands. I checked your live footprint: 30 Google creatives under Early Foods Pvt Ltd, plus a global storefront already live - strong setup for a clean-label brand.
 One finding: in baby food, parents are not choosing between brands - they are weighing the risk of trying you against a known multinational. Your ads and landing path lead with product; they should lead with reassurance: age-appropriate, full ingredient list, what is NOT inside, and other parents' faces.
-Attached: a 2-page audit with 3 fixes. Open to 15 minutes?
+Attached: the 7-page Paid Media and Measurement Audit. Open to 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -8802,7 +8802,7 @@
           <t>Hi team,
 I run paid-media audits for food brands out of Bengaluru. Over the last few days I inspected your live ad footprint - not a guess: Google Ads Transparency shows ~300 creatives under Delightful Gourmet Pvt Ltd, and I verified your Meta flight live in the Ad Library (Library ID 983369480870934, running since 15 Apr 2026).
 One finding you can act on today: that live Meta ad sends Bengaluru clicks to licious.in/store-locator. Buyers who tapped because of 'never frozen' arrive at a city picker - one full step before they see a product or price.
-I have attached a 2-page audit with 3 fixes, all doable without increasing spend. Worth 15 minutes?
+I have attached the 7-page Paid Media and Measurement Audit, all doable without increasing spend. Worth 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220
 P.S. The 0-4C cold-chain story is genuinely your strongest asset. It deserves to be the hero of the landing page, not just the ad.</t>
         </is>
@@ -8938,7 +8938,7 @@
           <t>Hi team,
 I run paid-media audits for food brands from Bengaluru. I inspected your live footprint: 35 Google creatives under Mimansa Industries Pvt Ltd - and 1M+ sourdoughs baked, which is the strongest trust proof in Indian sourdough.
 The leak: your paid clicks do not land on a 'where is my nearest loaf' page. For a brand in 300+ cities with quick-commerce distribution, that question is the whole conversion. The buyer asks it, does not get one-tap answer, and the aggregator keeps the relationship.
-Attached is a 2-page audit with 3 fixes. Open to a short call?
+Attached is the 7-page Paid Media and Measurement Audit. Open to a short call?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -9073,7 +9073,7 @@
           <t>Hi team,
 I audit paid media for Bengaluru food brands. I checked Google Ads Transparency for your domain this week and found zero live creatives - verified, on the Google side.
 For a brand with USD 112M raised and ~100 outlets, that means every 'coffee near me', 'cold brew delivery' and 'coffee beans online' query in your cities is answered by competitors. Local store campaigns are the cheapest walk-in channel a cafe chain can buy.
-I have attached a 2-page audit with 3 fixes, starting with the one I would run this month. To be clear about scope: this audit verifies Google - I have not claimed anything about your Meta inventory. Open to 15 minutes?
+I have attached the 7-page Paid Media and Measurement Audit, starting with the one I would run this month. To be clear about scope: this audit verifies Google - I have not claimed anything about your Meta inventory. Open to 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -9208,7 +9208,7 @@
 I audit paid media for Bengaluru food brands. I checked your live footprint: 11 Google creatives under Munchbox Frozen Foods Pvt Ltd, plus two brands (Frozen Bottle and Lubov Patisserie) and a franchise model with city and master-franchise pages.
 The gap: a single franchise sale is worth lakhs and the investor researches online first - but there is no structured paid funnel for franchise enquiries, and no store-radius campaigns for the outlets. Both are cheap to run and easy to measure.
 One small thing you can fix today: the footer links to /pages/faqs, but /pages/faq returns a 404.
-Attached is a 2-page audit with 3 fixes. Worth 15 minutes?
+Attached is the 7-page Paid Media and Measurement Audit. Worth 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220</t>
         </is>
       </c>
@@ -13908,9 +13908,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>meta ads:   live — running since 19 May 2026, 24 Jun 2026, 12 Aug 2026, 16 Sep 2026
-site root:  no meta pixel selector resolved on the crawl
-method:     single-method result — not asserted as absence</t>
+          <t>meta ads:    3 live creatives from the brand page (19 May and 24 Jun 2026)
+third-party:  Swiggy Instamart creative, 9 variants (12 Aug 2026)
+site root:   no meta pixel selector resolved on the crawl
+method:      single-method result — not asserted as absence</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -13940,9 +13941,9 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>creative observed:  Swiggy Instamart — organic protein, Insta-delivered
+          <t>creative observed:  Swiggy Instamart — Akshayakalpa paneer, 9 variants (12 Aug 2026)
 creative observed:  Zepto — quick-commerce placements under the term
-brand account:       separate creatives, running since May–Sep 2026</t>
+brand page:         3 creatives, running since 19 May 2026</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">

--- a/food-bangalore-audits/Food-Bangalore-ALL-IN-ONE.xlsx
+++ b/food-bangalore-audits/Food-Bangalore-ALL-IN-ONE.xlsx
@@ -19,12 +19,15 @@
     <sheet name="Opportunity Score" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Coverage (measured vs not)" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Evidence Register" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Verify These (links)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Cannot be verified" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leads'!$A$1:$O$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Emails'!$A$1:$F$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Findings (severity+evidence)'!$A$1:$F$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Evidence Register'!$A$1:$E$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Verify These (links)'!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +62,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="11">
@@ -140,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -176,6 +184,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -904,7 +915,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Placeholder international contact block on an India-facing site.</t>
+          <t>Placeholder international contact block on the Contact Us page.</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
@@ -2492,7 +2503,7 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
@@ -2517,15 +2528,15 @@
         </is>
       </c>
       <c r="C53" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Small live footprint; conversion path has a broken page.</t>
+          <t>Small live footprint; a stale FAQ URL and an unconfigured 404 template.</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
@@ -2558,7 +2569,7 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
@@ -2587,11 +2598,11 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Standard Shopify stack; one broken page observed.</t>
+          <t>Standard Shopify stack; stale URL variant and placeholder 404 template.</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
@@ -2624,7 +2635,7 @@
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
@@ -6893,6 +6904,1523 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E78"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Claim in the audit</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Where to check it</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>What you should see</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>≈400 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=akshayakalpa.org</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Around 400 creatives — the largest paid footprint in this set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>3 live Meta creatives from the brand page</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country: India)</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=active&amp;ad_type=all&amp;country=IN&amp;q=Akshayakalpa&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Three creatives from the Akshayakalpa page; the audit cites their running-since dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Meta IDs 2186726058790625 · 935934206094801 · 958522520368361</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library — individual ads</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?id=935934206094801</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Opens the creative running since 19 May 2026. Swap the id for either of the other two.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Swiggy Instamart runs Akshayakalpa product creative</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?id=3384075765110108</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>A Swiggy Instamart placement featuring Akshayakalpa paneer, 9 variants. This is third-party distribution, not the brand's own account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Contact Us page shows '0123.456.789 - 2 Queen Street, California'</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>akshayakalpa.org/contact-us</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>https://akshayakalpa.org/contact-us</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>The placeholder text sits at the top of the Contact Us page. Note the contrast: the homepage footer carries the correct Tiptur, Karnataka address, which is why the audit names the exact page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>No cache-control, no HSTS</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Response headers of akshayakalpa.org</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>https://securityheaders.com/?q=akshayakalpa.org</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Or from a terminal: curl -I https://akshayakalpa.org — neither header comes back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Akshayakalpa Organic</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>support@akshayakalpa.org</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>akshayakalpa.org FAQ and privacy policy</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>https://akshayakalpa.org/</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>The only official address the brand publishes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>58 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=anandsweets.in</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Around 58 creatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI ads pixel MsnBMqKgkHz42jqdSfTfFQ</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>anandsweets.in page source</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>https://anandsweets.in</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+U then Ctrl+F 'MsnBMqKgkHz42jqdSfTfFQ' — the OpenAI advertising pixel is in the storefront source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>HSTS, CSP, X-Frame-Options all present</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Response headers</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>https://securityheaders.com/?q=anandsweets.in</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>All four header families return a pass — the strongest posture in this set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>4.4 rating from 250 reviews</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>anandsweets.in structured data</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>https://anandsweets.in</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F 'aggregateRating' in the page source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Anand Sweets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>care@anandsweets.net</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>anandsweets.in footer / contact</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>https://www.anandsweets.in/</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Published in the site footer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>3 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=milkymist.com</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Around 3 creatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Wix behind Varnish</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Response headers</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>https://securityheaders.com/?q=milkymist.com</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Server headers show Varnish and Wix identifiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Milky Mist</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>customercare@milkymist.com</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>milkymist.com/reach-us</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>https://milkymist.com/reach-us</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Published on the reach-us page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>1 live Google creative</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=idfreshfood.com</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>A single creative — the finding that drives this audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Access-Control-Allow-Origin: *</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Response headers</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>https://securityheaders.com/?q=idfreshfood.com</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Or: curl -I https://idfreshfood.com — the wildcard CORS header is returned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>LiteSpeed cache HIT</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Response headers</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>https://securityheaders.com/?q=idfreshfood.com</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>The cache header reports a hit, confirming the cache layer works.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>customercare@idfreshfood.com</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>idfreshfood.com/contact-us</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>https://idfreshfood.com/contact-us</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Published on the contact page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>iD Fresh Food</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>FY25 revenue ≈Rs 681.4 Cr, PAT ≈Rs 25.87 Cr</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Published FY25 results as reported</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>https://idfreshfood.com/</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Figures are quoted as reported, not audited by us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>56 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=chaipoint.com</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Around 56 creatives, under Mountain Trail Foods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>GA4 G-EN77D2S0YH on the site root</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>chaipoint.com page source</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>https://chaipoint.com</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+U then Ctrl+F 'G-EN77D2S0YH'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>900,000+ cups a day · 150+ stores · 8,100+ workplaces</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>chaipoint.com structured data (JSON-LD)</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>https://chaipoint.com</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F 'cups' or '900' in the page source; the figures are in the machine-readable JSON-LD block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Static build on Amazon S3 + CloudFront</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Response headers</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>https://securityheaders.com/?q=chaipoint.com</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Server headers show cloudfront and S3 asset hosting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>customercare@chaipoint.com</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Chai Point help centre</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>https://shop.chaipoint.com/</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Published on the order site's help section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>77 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=cothas.com</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Around 77 creatives, under Freeflow Creative Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Tag layer unconfirmed</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Chrome DevTools on cothas.com</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>https://cothas.com</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>This is the one claim you can settle in a browser: open DevTools → Network, filter 'collect' or 'gtm', and reload. If tags fire, the audit's 'unconfirmed' wording is exactly right — and the fix is simply to confirm it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>customercare@cothas.com</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>cothas.com/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>https://cothas.com/pages/contact-us</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Published on the contact page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Founded 1948, Jigani facility</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Cothas Coffee — own pages</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>https://cothas.com/</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Stated on the brand's own site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>30 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Around 30 creatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Shopify theme 124761112618 behind Cloudflare</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Response headers + page source</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>https://earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Cloudflare reported in the server headers; the theme ID appears in the storefront source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Early Foods</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>hello@earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>earlyfoods.com</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>https://earlyfoods.com/</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Published on the site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>≈300 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=licious.in</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>The page header reads approximately 300 ads, under Delightful Gourmet Pvt Ltd (Verified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>≈550 live Meta ads</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library (country: India)</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?active_status=active&amp;ad_type=all&amp;country=IN&amp;q=Licious&amp;search_type=keyword_unordered</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Around 550 results for the brand term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Meta library ID 983369480870934</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Meta Ad Library — the ad itself</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ads/library/?id=983369480870934</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>The specific Licious ad referenced in the audit, with its running-since date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>GTM-KVBCJN · GA4 G-YN0TX18PEE · Ads AW-871318622</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>licious.in page source</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>https://licious.in</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Open the page, press Ctrl+U (view source), then Ctrl+F each ID. All four appear, including Meta pixel 378591842535023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>FY25 revenue ≈Rs 795 Cr, loss ≈Rs 218.3 Cr</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>licious.in — published company results</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>https://www.licious.in/</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Published in the company's reported FY25 results. This is a third-party reported figure, quoted as reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Licious</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>talktous@licious.com</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>licious.in support / contact page</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>https://www.licious.in/</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Publish in the site's contact or help section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>35 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=thebakersdozen.in</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Around 35 creatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>GTM-MQQF2MXB · Ads AW-618150299</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>thebakersdozen.in page source</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>https://thebakersdozen.in</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F each ID in the page source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Meta pixel 3996239487069441</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>thebakersdozen.in page source</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>https://thebakersdozen.in</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+F '3996239487069441'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>No HSTS, no cache-control, no security headers</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Response headers</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>https://securityheaders.com/?q=thebakersdozen.in</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Most or all headers return a fail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>The Baker's Dozen</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>fresh@thebakersdozen.in</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>thebakersdozen.in/contact-us</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>https://thebakersdozen.in/contact-us</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Published on the contact page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Title tag is the domain string</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>thirdwavecoffeeroasters.com page source</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>https://thirdwavecoffeeroasters.com</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Ctrl+U and look at the first line inside &lt;head&gt;: the title reads 'www.thirdwavecoffeeroasters.com' instead of the brand name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>0 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=thirdwavecoffeeroasters.com</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>No creatives are returned for the domain. The audit states this as measured on one day for this domain, not as a claim about the whole account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Third Wave Coffee</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>orders@thirdwavecoffee.in</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>thirdwavecoffee.in/pages/contact</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>https://thirdwavecoffee.in/pages/contact</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Published on the contact page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>11 live Google creatives</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Google Ads Transparency Center (region: India)</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>https://adstransparency.google.com/?region=IN&amp;domain=frozenbottle.com</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Around 11 creatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>A stale FAQ URL returns 404</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>frozenbottle.com/pages/faq vs the live /pages/faqs</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>https://frozenbottle.com/pages/faq</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>The singular URL returns 'not found'. The working FAQ is the plural one: frozenbottle.com/pages/faqs — the audit states both, so you can see exactly what is and is not broken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Frozen Bottle</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>vipul@frozenbottle.in</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>frozenbottle.com footer (partnership section)</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>https://frozenbottle.com/</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Published under collaboration and partnership in the footer.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E50"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId49"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Why no public source exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Ad spend (Rs/month)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>No public source exists. Ad platforms do not disclose spend for commercial advertisers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ROAS and CPA</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Only visible inside the advertiser's own ad accounts and analytics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Conversion rates</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Private to the advertiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Internal revenue splits by channel</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Private to the advertiser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Rule applied in every audit</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Where a value could not be measured it is reported as unavailable or not measured. Nothing has been inferred to fill a gap, and no tag is described as absent unless a second method confirmed it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7855,7 +9383,7 @@
         <is>
           <t>Hi team,
 I audit paid media for food brands from Bengaluru. Your footprint is the biggest I found in this category: ~400 live Google creatives under Akshayakalpa Farms and Foods Pvt Ltd. The product story behind it is world-class - 4C farm chilling, 24-36 hours to doorstep vs the 72-96 hour industry norm, APEDA certified.
-One thing you can check in 30 seconds: the footer of akshayakalpa.org currently contains template placeholder text - '0123.456.789 - 2 Queen Street, California, USA'. Your paid traffic lands on that page. It is a small fix and a direct trust cost while it is live.
+One thing you can check in 30 seconds: the Contact Us page at akshayakalpa.org/contact-us currently contains template placeholder text - '0123.456.789 - 2 Queen Street, California, USA'. Your paid traffic lands on that page. It is a small fix and a direct trust cost while it is live.
 Attached is the 7-page Paid Media and Measurement Audit, including what I would do with ~400 creatives to make them learn faster than they spend. Worth 15 minutes?
 - Smart Pursuit, Bengaluru | 7095024220
 P.S. I am writing to your published support address because the site does not list a marketing or partner contact - that is itself one of the findings.</t>
@@ -9402,7 +10930,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Live footer template text - '0123.456.789 - 2 Queen Street, California, USA' - sits on the pages paid traffic lands on. Small fix, direct trust cost while live.</t>
+          <t>Live Contact Us template text - '0123.456.789 - 2 Queen Street, California, USA' - sits on a page paid traffic can land on. Small fix, direct trust cost while live.</t>
         </is>
       </c>
     </row>
@@ -12247,7 +13775,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Placeholder footer live</t>
+          <t>Placeholder contact block live</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -13148,7 +14676,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>akshayakalpa.org (FAQ, company, privacy policy, contact pages): 4C farm chilling, 24-36 hr delivery claim, APEDA + Jaivik Bharat certification, farm locations, support@akshayakalpa.org / +91-9535388122, and live footer placeholder text.</t>
+          <t>akshayakalpa.org (FAQ, company, privacy policy, contact pages): 4C farm chilling, 24-36 hr delivery claim, APEDA + Jaivik Bharat certification, farm locations, support@akshayakalpa.org / +91-9535388122, and live Contact Us page placeholder text.</t>
         </is>
       </c>
     </row>
@@ -13838,19 +15366,19 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>The site footer carries an international placeholder phone number and address</t>
+          <t>The Contact Us page carries an international template placeholder</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>footer text:  0123.456.789 – 2 Queen Street, California
-site:        akshayakalpa.org (India-facing)
-published:   Tiptur farms, Karnataka; corporate office Bengaluru</t>
+          <t>page:      akshayakalpa.org/contact-us
+text:      "0123.456.789 - 2 Queen Street,California, USA"
+homepage:  correct Tiptur, Karnataka address published</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>A placeholder contact block on a site taking dairy subscriptions actively damages trust and is trivially fixable. Every other finding in this report is secondary to it.</t>
+          <t>The Contact Us page a paid visitor can reach still shows a US placeholder phone number and address, while the site footer shows the correct Tiptur address. On a site selling dairy subscriptions, that inconsistency costs trust and takes minutes to correct.</t>
         </is>
       </c>
     </row>
@@ -15457,19 +16985,18 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>The FAQ page returns a 404 error</t>
+          <t>Eleven live creatives is below the learning threshold for this category</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>url:    frozenbottle.com/pages/faq
-status: HTTP 404
-context: linked from the storefront navigation</t>
+          <t>google creatives live: ≈11 (region India)
+category:              desserts, ice cream and gifting</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>Frequently-asked questions are where dessert and gifting customers resolve delivery doubts. A dead page is a lost order, and on Shopify it is usually a two-minute fix.</t>
+          <t>Eleven creatives across any meaningful audience set will not separate creative from audience effects. Two clean tests would tell more than eleven undifferentiated ads.</t>
         </is>
       </c>
     </row>
@@ -15482,25 +17009,27 @@
       <c r="B54" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Eleven live creatives is below the learning threshold for this category</t>
+          <t>A stale FAQ URL returns 404, and the 404 template still shows placeholder products</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>google creatives live: ≈11 (region India)
-category:              desserts, ice cream and gifting</t>
+          <t>url:           frozenbottle.com/pages/faq → HTTP 404
+live FAQ:      frozenbottle.com/pages/faqs (plural) works
+404 template:  'Example product $29' cards still render
+homepage:      links only to the working plural URL</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>Eleven creatives across any meaningful audience set will not separate creative from audience effects. Two clean tests would tell more than eleven undifferentiated ads.</t>
+          <t>The live FAQ is reachable, so no customer is blocked today. What remains is a stale URL that should redirect to the working one, and a 404 template still showing unconfigured Shopify placeholder cards. Both are minutes of theme work, and both are visible the moment a paid visitor mistypes a link.</t>
         </is>
       </c>
     </row>
